--- a/www/download/IND.surplus_value.empe_ms.r.pc.rpO2.xlsx
+++ b/www/download/IND.surplus_value.empe_ms.r.pc.rpO2.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-84.02</t>
+          <t>-0.840157417229105</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-84.55</t>
+          <t>-0.845490934111972</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-79.6</t>
+          <t>-0.795997168652186</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-80.28</t>
+          <t>-0.802846287308245</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-87.47</t>
+          <t>-0.874714390752705</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-89.95</t>
+          <t>-0.899511211566184</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-88.68</t>
+          <t>-0.886758694891155</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-90.36</t>
+          <t>-0.903612986223686</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-90.47</t>
+          <t>-0.904724165785576</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-87.04</t>
+          <t>-0.87039203438975</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>-91.49</t>
+          <t>-0.91492490026702</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>-92.03</t>
+          <t>-0.920266997647104</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-92.32</t>
+          <t>-0.923228603288607</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-91.34</t>
+          <t>-0.913384402698037</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-88.11</t>
+          <t>-0.881092769832915</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-83.95</t>
+          <t>-0.839466135717796</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-84.64</t>
+          <t>-0.846388025835667</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-77.14</t>
+          <t>-0.77140605135308</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-79.46</t>
+          <t>-0.794587542061664</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-84.03</t>
+          <t>-0.840326302922615</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-87.82</t>
+          <t>-0.878204763239915</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-88.9</t>
+          <t>-0.888999969251702</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-88.75</t>
+          <t>-0.887455077122585</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-88.44</t>
+          <t>-0.884396371588421</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-88.54</t>
+          <t>-0.885379401051906</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>-90.36</t>
+          <t>-0.903600617917706</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>-91.32</t>
+          <t>-0.913236785939656</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>-89.39</t>
+          <t>-0.893915278473852</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>-88.27</t>
+          <t>-0.882703807910431</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>-83.28</t>
+          <t>-0.832802832303475</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-79.62</t>
+          <t>-0.796173622810814</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-76.61</t>
+          <t>-0.766144989557936</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-70.03</t>
+          <t>-0.700261252337422</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-71.65</t>
+          <t>-0.716450294495929</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-77.3</t>
+          <t>-0.773039880527274</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-84.18</t>
+          <t>-0.841797242063861</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-84.87</t>
+          <t>-0.848717710911928</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-86.44</t>
+          <t>-0.864433487845195</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-87.73</t>
+          <t>-0.877293317592664</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-87.97</t>
+          <t>-0.879701185144381</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-89.98</t>
+          <t>-0.899832484944958</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>-89.34</t>
+          <t>-0.893385461833469</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>-87.06</t>
+          <t>-0.870619835838988</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>-86.99</t>
+          <t>-0.86990003129843</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>-82.82</t>
+          <t>-0.828176802108588</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>15.12</t>
+          <t>0.151166469726977</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>36.37</t>
+          <t>0.363702324266511</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>100.06</t>
+          <t>1.00060694814924</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>50.25</t>
+          <t>0.502482497524061</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>27.26</t>
+          <t>0.272588615802861</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>7.19</t>
+          <t>0.0719389820233354</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>-0.0650254782717508</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-18.88</t>
+          <t>-0.188829747289739</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>-8.43</t>
+          <t>-0.0842955474080515</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-39.78</t>
+          <t>-0.397844829661593</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>-44.09</t>
+          <t>-0.440892012732816</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>-52.49</t>
+          <t>-0.524904307742104</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>-46.93</t>
+          <t>-0.469260325059004</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>-38.45</t>
+          <t>-0.384506101931383</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>-28.75</t>
+          <t>-0.287511772161052</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>167.7</t>
+          <t>1.67702490054749</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>169.09</t>
+          <t>1.69085112580741</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>194.14</t>
+          <t>1.94137591512212</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>185.36</t>
+          <t>1.8535664290053</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>196.31</t>
+          <t>1.96313493708487</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>98.85</t>
+          <t>0.988513067624171</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>93.64</t>
+          <t>0.936400614811147</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>123.3</t>
+          <t>1.23299932919714</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>117.88</t>
+          <t>1.17877397817959</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>95.53</t>
+          <t>0.955280083014075</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>80.29</t>
+          <t>0.802948983791157</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>70.65</t>
+          <t>0.706535872632387</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>81.13</t>
+          <t>0.811295413834934</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>72.53</t>
+          <t>0.725265337388614</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>133.48</t>
+          <t>1.33481911900172</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-61.75</t>
+          <t>-0.617469027325604</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-61.58</t>
+          <t>-0.615835176969359</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-56.56</t>
+          <t>-0.565615875255549</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-62.63</t>
+          <t>-0.62626007586175</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-70.29</t>
+          <t>-0.702885464136984</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-81.64</t>
+          <t>-0.816414051457618</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-83.11</t>
+          <t>-0.831064324461499</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-80.74</t>
+          <t>-0.807410850957702</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>-82.23</t>
+          <t>-0.822274295609934</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-81.73</t>
+          <t>-0.81731486794954</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>-85.82</t>
+          <t>-0.85820678165755</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>-84.99</t>
+          <t>-0.84989765117776</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>-81.58</t>
+          <t>-0.815829268856798</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>-80.1</t>
+          <t>-0.800980473208061</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>-72.86</t>
+          <t>-0.728616127089575</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-28.39</t>
+          <t>-0.283902629499654</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-26.88</t>
+          <t>-0.268810348424564</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-22.74</t>
+          <t>-0.227352478470278</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-19.56</t>
+          <t>-0.195570341620951</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-17.37</t>
+          <t>-0.173728031287103</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-18.89</t>
+          <t>-0.188936471579515</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-12.75</t>
+          <t>-0.127524451605192</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-7.93</t>
+          <t>-0.0792650315473112</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-0.0316367392923895</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>-0.0110363047124956</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>0.0145826645314755</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>0.0465673235273178</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>0.190800287945778</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>19.64</t>
+          <t>0.19642270526793</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>29.77</t>
+          <t>0.297660301797796</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-54.04</t>
+          <t>-0.540389323940002</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-60.97</t>
+          <t>-0.609744112019705</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>-36.88</t>
+          <t>-0.368794001888073</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-48.18</t>
+          <t>-0.481812901702442</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-67.18</t>
+          <t>-0.671833959703966</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-74.57</t>
+          <t>-0.745696343237858</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-77.56</t>
+          <t>-0.775556414007076</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-78.68</t>
+          <t>-0.786813325629188</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-78.35</t>
+          <t>-0.783492055955926</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-76.05</t>
+          <t>-0.760504807376096</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>-69.82</t>
+          <t>-0.698204644689033</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>-64.1</t>
+          <t>-0.641049539618897</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>-60.13</t>
+          <t>-0.601299760194789</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>-53.69</t>
+          <t>-0.536924987608686</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-0.114517229421625</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>0.0166529334112469</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-41.87</t>
+          <t>-0.418737576008839</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>-13.48</t>
+          <t>-0.134754444949187</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-28.44</t>
+          <t>-0.284393151288706</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-44.12</t>
+          <t>-0.44121699934854</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-57.63</t>
+          <t>-0.576279531868171</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-68.98</t>
+          <t>-0.689800124201651</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-71.32</t>
+          <t>-0.713202491157628</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>-74.57</t>
+          <t>-0.745666792277566</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-74</t>
+          <t>-0.740040629518313</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>-78.22</t>
+          <t>-0.782189512550981</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>-78.43</t>
+          <t>-0.784331066556556</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>-73.25</t>
+          <t>-0.732515339857139</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>-70.42</t>
+          <t>-0.704240187855024</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>-49.83</t>
+          <t>-0.498337780591475</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-86.95</t>
+          <t>-0.869457197839688</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-85.39</t>
+          <t>-0.853888192752223</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>-82.85</t>
+          <t>-0.828450075103087</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-84.26</t>
+          <t>-0.842622454412023</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-88.08</t>
+          <t>-0.880784673202612</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-91.6</t>
+          <t>-0.91603577026417</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-92.5</t>
+          <t>-0.925048747408579</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-92.46</t>
+          <t>-0.924626095779911</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>-92.85</t>
+          <t>-0.928479390753143</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-92.55</t>
+          <t>-0.925547621879528</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>-93</t>
+          <t>-0.92997924988752</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>-93.35</t>
+          <t>-0.933451214743942</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>-91.49</t>
+          <t>-0.914881439895082</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>-90.53</t>
+          <t>-0.905257360010836</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>-86.74</t>
+          <t>-0.867431533160197</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-91.63</t>
+          <t>-0.916256150229192</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-91.16</t>
+          <t>-0.911623387510143</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>-87.24</t>
+          <t>-0.872409932730123</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-88.01</t>
+          <t>-0.88011290399396</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-89.38</t>
+          <t>-0.893847800159379</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-90.88</t>
+          <t>-0.908786247809011</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-91.6</t>
+          <t>-0.915975531415557</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-92.14</t>
+          <t>-0.921393706917804</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>-92.9</t>
+          <t>-0.928980788973072</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-93.09</t>
+          <t>-0.930905616382539</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>-93.79</t>
+          <t>-0.937924816518722</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>-93.64</t>
+          <t>-0.936428928702995</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>-92.47</t>
+          <t>-0.92473344070142</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>-93</t>
+          <t>-0.930038407027758</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>-88.18</t>
+          <t>-0.881772203152557</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-70.89</t>
+          <t>-0.708854431502931</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-71.49</t>
+          <t>-0.714905483027807</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>-66.1</t>
+          <t>-0.661009660209215</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-68.87</t>
+          <t>-0.688681240577681</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-77.61</t>
+          <t>-0.776117166685786</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-85.2</t>
+          <t>-0.852017031559623</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-85.88</t>
+          <t>-0.858788704932842</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-85.41</t>
+          <t>-0.854131465117994</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>-85.58</t>
+          <t>-0.855750776269429</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-87.43</t>
+          <t>-0.874270302731423</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>-89.4</t>
+          <t>-0.893986715795593</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>-90.04</t>
+          <t>-0.900423375915434</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>-87.81</t>
+          <t>-0.878135250070181</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>-87.03</t>
+          <t>-0.870256622766249</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>-80.44</t>
+          <t>-0.804396854763115</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>327.85</t>
+          <t>3.27848075685389</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>298.51</t>
+          <t>2.98509597073167</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>494.34</t>
+          <t>4.9434461097918</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>454.01</t>
+          <t>4.5401362427614</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-15.23</t>
+          <t>-0.152324111818026</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-71.83</t>
+          <t>-0.718272814875779</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-73.29</t>
+          <t>-0.732914338134955</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-79.88</t>
+          <t>-0.798848999123406</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>-87.53</t>
+          <t>-0.875327756241279</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-79.38</t>
+          <t>-0.793761367816505</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>-66.59</t>
+          <t>-0.665931370423391</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>-76.98</t>
+          <t>-0.76980861341267</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>-81.2</t>
+          <t>-0.812032617743025</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>-81.73</t>
+          <t>-0.817329365797264</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>-73.83</t>
+          <t>-0.738320332031861</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-76.24</t>
+          <t>-0.762367689667971</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-76.86</t>
+          <t>-0.76864850898065</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>-67.24</t>
+          <t>-0.672403449005975</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-71.16</t>
+          <t>-0.71163139214798</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-78.38</t>
+          <t>-0.783788583608791</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-81.9</t>
+          <t>-0.819038146461186</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-84.4</t>
+          <t>-0.844011195657084</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-84.71</t>
+          <t>-0.847056306690315</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>-88.3</t>
+          <t>-0.8830068744167</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-88.41</t>
+          <t>-0.884074807333851</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>-88.99</t>
+          <t>-0.889880957353826</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>-89.29</t>
+          <t>-0.892944249015671</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>-86.67</t>
+          <t>-0.866684921822271</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>-86.1</t>
+          <t>-0.860986209400265</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>-79.04</t>
+          <t>-0.790401381925431</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-87.15</t>
+          <t>-0.871457754084554</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-86.12</t>
+          <t>-0.861207739532848</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>-83.11</t>
+          <t>-0.831061956046221</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-83.63</t>
+          <t>-0.836344206054262</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-87.85</t>
+          <t>-0.878501333381349</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-91.33</t>
+          <t>-0.913330145708953</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-91.89</t>
+          <t>-0.918907420298399</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-92.34</t>
+          <t>-0.923417368896778</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>-93.07</t>
+          <t>-0.930748581867073</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-93.69</t>
+          <t>-0.936872016511329</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>-94.79</t>
+          <t>-0.947940424057125</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>-94.84</t>
+          <t>-0.948437040897309</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>-93.64</t>
+          <t>-0.936444905617639</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>-93.21</t>
+          <t>-0.932079414677156</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>-89.94</t>
+          <t>-0.89939530592358</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-86.21</t>
+          <t>-0.862130121564607</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-85.27</t>
+          <t>-0.852667628747142</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>-79.86</t>
+          <t>-0.798626733928688</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-81.23</t>
+          <t>-0.812296508647847</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-85.86</t>
+          <t>-0.85863042058176</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-89.31</t>
+          <t>-0.89309613764436</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-90.31</t>
+          <t>-0.903109054021778</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-90.3</t>
+          <t>-0.902965395976634</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>-91.27</t>
+          <t>-0.912690265568936</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-91.57</t>
+          <t>-0.915727326166646</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>-92.6</t>
+          <t>-0.925953007172041</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>-93.03</t>
+          <t>-0.930332207853551</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>-92.27</t>
+          <t>-0.922724164496386</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>-91.25</t>
+          <t>-0.912496983926614</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>-88.48</t>
+          <t>-0.884817305842268</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-22.69</t>
+          <t>-0.226919926486525</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>-31.21</t>
+          <t>-0.312130060144666</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>-9.93</t>
+          <t>-0.0992611318368884</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-21.5</t>
+          <t>-0.214986235502093</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-44.47</t>
+          <t>-0.444722664555478</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-69.54</t>
+          <t>-0.695367861013358</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-73.85</t>
+          <t>-0.738521064297143</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-76.15</t>
+          <t>-0.761470599871717</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>-79.38</t>
+          <t>-0.793804615329675</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-77.33</t>
+          <t>-0.773328312369011</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>-84.19</t>
+          <t>-0.841927375657534</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>-87.01</t>
+          <t>-0.870050371025399</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>-84.38</t>
+          <t>-0.843765851394748</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>-83.21</t>
+          <t>-0.832063102428699</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>-75.72</t>
+          <t>-0.757201346378086</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-29.3</t>
+          <t>-0.293031933426154</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>-20.92</t>
+          <t>-0.209216181090323</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>7.29</t>
+          <t>0.0728562574034792</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-16.1</t>
+          <t>-0.161028271685548</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-36.92</t>
+          <t>-0.369208653544521</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-42.72</t>
+          <t>-0.427183851022547</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-55.77</t>
+          <t>-0.557650398348507</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-54.87</t>
+          <t>-0.548654567924979</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>-62.08</t>
+          <t>-0.62079332705406</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-62.59</t>
+          <t>-0.625867286924557</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>-64.73</t>
+          <t>-0.647269995449378</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>-61.99</t>
+          <t>-0.619918320366438</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>-58.23</t>
+          <t>-0.582334112695095</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>-41.64</t>
+          <t>-0.416390865259158</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>0.0334794166672967</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>132.83</t>
+          <t>1.32830514637194</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>139.61</t>
+          <t>1.39607908142345</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>141.43</t>
+          <t>1.41429073351068</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>178.61</t>
+          <t>1.7861353302706</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>97.24</t>
+          <t>0.972431791707557</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>41.63</t>
+          <t>0.416287558815368</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>0.278177834343364</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>0.203851978935415</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>15.97</t>
+          <t>0.159745326859826</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>0.0716419139119231</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>12.22</t>
+          <t>0.122172370864585</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>15.39</t>
+          <t>0.153896459236311</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>0.296254786838436</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>23.06</t>
+          <t>0.230564818214242</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>61.53</t>
+          <t>0.615338141348571</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>149.35</t>
+          <t>1.49346099851126</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>169.34</t>
+          <t>1.69344612983954</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>162.71</t>
+          <t>1.6270727650248</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>164.16</t>
+          <t>1.64157189719908</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>135.22</t>
+          <t>1.35223740389359</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>131.38</t>
+          <t>1.31383750040664</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>146.44</t>
+          <t>1.46437989610822</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>162.41</t>
+          <t>1.6241217926612</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>179.7</t>
+          <t>1.7970078461165</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>187.79</t>
+          <t>1.87787996550455</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>187.3</t>
+          <t>1.87301419832646</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>190.06</t>
+          <t>1.90055913180031</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>200.48</t>
+          <t>2.00476295008672</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>220.43</t>
+          <t>2.20432205719235</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>233.51</t>
+          <t>2.33511022349007</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-71.53</t>
+          <t>-0.715310780047071</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-68.78</t>
+          <t>-0.687818871814097</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>-74.98</t>
+          <t>-0.749774686860856</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-76.37</t>
+          <t>-0.763661859526774</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-79.74</t>
+          <t>-0.797407235672345</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-84</t>
+          <t>-0.839989075689461</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-83.8</t>
+          <t>-0.838031643759925</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-84.42</t>
+          <t>-0.844168647633015</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>-87.11</t>
+          <t>-0.871127493381395</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-89.13</t>
+          <t>-0.891251006681596</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>-90.9</t>
+          <t>-0.908963383964418</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>-91.24</t>
+          <t>-0.912435527797614</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>-90.08</t>
+          <t>-0.900792626332722</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>-88.76</t>
+          <t>-0.887551923778398</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>-87.92</t>
+          <t>-0.879210034316528</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-67.08</t>
+          <t>-0.670837451137225</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-67.42</t>
+          <t>-0.67421414024799</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-61.59</t>
+          <t>-0.615929022075296</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-62.51</t>
+          <t>-0.625098982182522</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-71.77</t>
+          <t>-0.717705150663951</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-79.68</t>
+          <t>-0.796779858914798</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-81.63</t>
+          <t>-0.816280944999768</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-82.28</t>
+          <t>-0.822803079511729</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-81.14</t>
+          <t>-0.811442533995769</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-83.84</t>
+          <t>-0.838448560105356</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>-86.73</t>
+          <t>-0.867347475854034</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>-88.22</t>
+          <t>-0.882215719534973</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>-85.86</t>
+          <t>-0.858592123452682</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>-85.41</t>
+          <t>-0.854074057251301</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>-79.31</t>
+          <t>-0.793080157903382</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-67.99</t>
+          <t>-0.679920601708282</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-68.18</t>
+          <t>-0.681772624076842</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>-60.45</t>
+          <t>-0.60452642406825</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-56.62</t>
+          <t>-0.566246353134418</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-70.56</t>
+          <t>-0.7055779712231</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-77.67</t>
+          <t>-0.776725598640136</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-78.78</t>
+          <t>-0.787809400569049</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-78.98</t>
+          <t>-0.789795470456993</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>-81.38</t>
+          <t>-0.813793980030881</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-82.25</t>
+          <t>-0.822501223316856</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>-84.58</t>
+          <t>-0.845763523926005</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>-84.42</t>
+          <t>-0.844205343812401</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>-80.34</t>
+          <t>-0.803380252775722</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>-81.7</t>
+          <t>-0.817030574501268</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>-74.68</t>
+          <t>-0.7468293927912</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-63.3</t>
+          <t>-0.633017113425986</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-63.74</t>
+          <t>-0.637437427013191</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>-61.76</t>
+          <t>-0.617599836302751</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-53.03</t>
+          <t>-0.530265263032507</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-68.32</t>
+          <t>-0.683174403026041</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-80.44</t>
+          <t>-0.804397511807584</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-79.82</t>
+          <t>-0.798215688559527</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-76.27</t>
+          <t>-0.762712878008248</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>-78.88</t>
+          <t>-0.788846276256172</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-77.7</t>
+          <t>-0.777009897954797</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>-81.03</t>
+          <t>-0.810280993256656</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>-82.06</t>
+          <t>-0.820612492368528</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>-78.2</t>
+          <t>-0.782017528320655</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>-77.9</t>
+          <t>-0.778991148840116</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>-67.92</t>
+          <t>-0.679166501143051</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>-31.15</t>
+          <t>-0.311531968577994</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>-50.75</t>
+          <t>-0.507506998285588</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>-53.13</t>
+          <t>-0.53131941480387</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-45.35</t>
+          <t>-0.453509878966866</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-52.16</t>
+          <t>-0.521603027305168</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-57.76</t>
+          <t>-0.577575480117615</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>-72.9</t>
+          <t>-0.729041166266561</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>-67.16</t>
+          <t>-0.671581919924682</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>-72.98</t>
+          <t>-0.729820755268414</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-79</t>
+          <t>-0.789964340328895</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>-82.19</t>
+          <t>-0.821853434186785</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>-82.26</t>
+          <t>-0.822565334295297</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>-87.65</t>
+          <t>-0.876488720017394</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>-84.07</t>
+          <t>-0.840692710657485</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>-64.15</t>
+          <t>-0.64153585396157</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>-77.21</t>
+          <t>-0.772100268719556</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-84.76</t>
+          <t>-0.847580385425714</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>-82.66</t>
+          <t>-0.826641402709035</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-83.97</t>
+          <t>-0.839686507075086</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-87.35</t>
+          <t>-0.873524929019119</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-91.22</t>
+          <t>-0.912208636224834</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-91.53</t>
+          <t>-0.915318846053886</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-90.34</t>
+          <t>-0.90335912176085</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>-91.22</t>
+          <t>-0.912224201342145</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-90.9</t>
+          <t>-0.909047092151476</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>-92.6</t>
+          <t>-0.926037759150812</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>-92.55</t>
+          <t>-0.92554758769939</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>-91.04</t>
+          <t>-0.910408928151051</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>-90.06</t>
+          <t>-0.900640509116042</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>-88.28</t>
+          <t>-0.882805089913284</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>0.263992189757378</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>13.16</t>
+          <t>0.131588793568143</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>26.36</t>
+          <t>0.263646461605408</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>0.0171204551006465</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-15.54</t>
+          <t>-0.155422537787907</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-26.4</t>
+          <t>-0.263963196819474</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-49.06</t>
+          <t>-0.490563457321563</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>-42.69</t>
+          <t>-0.426903290441554</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>-33.45</t>
+          <t>-0.334530797506205</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>64.03</t>
+          <t>0.640306883286595</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>660.67</t>
+          <t>6.60666501679996</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>210.84</t>
+          <t>2.10842726984919</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>-71.09</t>
+          <t>-0.710909949270502</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>-67.62</t>
+          <t>-0.676210639440375</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>-50.84</t>
+          <t>-0.508411850517231</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>214.92</t>
+          <t>2.14920419882866</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>222.59</t>
+          <t>2.22587970941173</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>241.82</t>
+          <t>2.41817397634407</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>181.57</t>
+          <t>1.8156957320464</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>121.84</t>
+          <t>1.2184320590636</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>59.75</t>
+          <t>0.597502562647273</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>28.59</t>
+          <t>0.285871967547755</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>28.74</t>
+          <t>0.28737336504319</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>42.96</t>
+          <t>0.429649570656335</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>57.06</t>
+          <t>0.570566998311143</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>32.28</t>
+          <t>0.322774933785654</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>0.319014437235359</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>51.34</t>
+          <t>0.513393663910444</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>0.807991601062984</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>161.71</t>
+          <t>1.61708756148798</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>34.14</t>
+          <t>0.34138689321345</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>13.75</t>
+          <t>0.137520836429634</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>150.18</t>
+          <t>1.50177125647451</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>0.487525926675904</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.00589542333688231</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-18.17</t>
+          <t>-0.181744678369102</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>-53.62</t>
+          <t>-0.536219051360297</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>-51</t>
+          <t>-0.509991172002829</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>-39.49</t>
+          <t>-0.394900610763516</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-43.42</t>
+          <t>-0.434234964145016</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>-37.9</t>
+          <t>-0.378958923379925</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>-44.01</t>
+          <t>-0.440076477513249</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>-25.58</t>
+          <t>-0.255830717314234</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>-13.18</t>
+          <t>-0.13180706249319</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>0.20983458963979</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>-92.18</t>
+          <t>-0.921772094688829</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-92.26</t>
+          <t>-0.922604778434151</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>-87.93</t>
+          <t>-0.879278691746621</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-90.65</t>
+          <t>-0.906497742704122</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-92.11</t>
+          <t>-0.921120357522523</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-93.73</t>
+          <t>-0.93728866931624</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-93.69</t>
+          <t>-0.936912751827229</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-93.48</t>
+          <t>-0.934804560743582</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-94.1</t>
+          <t>-0.941003298758826</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-94.31</t>
+          <t>-0.943096343210213</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>-94.99</t>
+          <t>-0.949909755328089</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-94.92</t>
+          <t>-0.949193636666068</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>-94.27</t>
+          <t>-0.942744848414183</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-93.82</t>
+          <t>-0.938168015120042</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>-91.98</t>
+          <t>-0.91982070932353</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>-17.99</t>
+          <t>-0.179886551057528</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>-27.4</t>
+          <t>-0.27396514764761</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>-13.37</t>
+          <t>-0.133678929718592</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-33.8</t>
+          <t>-0.337963356118015</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-39.84</t>
+          <t>-0.398414755825581</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-51.27</t>
+          <t>-0.512744226936162</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>-39.45</t>
+          <t>-0.394475416099037</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>-36.19</t>
+          <t>-0.361893879886209</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>-34.94</t>
+          <t>-0.349354694304641</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-38.71</t>
+          <t>-0.387059129824993</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>-40.65</t>
+          <t>-0.406511567749557</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>-42.55</t>
+          <t>-0.425517712343009</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>-41.98</t>
+          <t>-0.419790613048843</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>-42.68</t>
+          <t>-0.426785835211918</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>-28.54</t>
+          <t>-0.285382282880975</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>-56.88</t>
+          <t>-0.568767538688512</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-57.71</t>
+          <t>-0.5770781825271</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>-45.13</t>
+          <t>-0.451270061587235</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-51.59</t>
+          <t>-0.515911403580536</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-63.79</t>
+          <t>-0.637857205741635</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-76.99</t>
+          <t>-0.76989120485076</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>-77.68</t>
+          <t>-0.776827282613153</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>-77.27</t>
+          <t>-0.772691792225892</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>-72.65</t>
+          <t>-0.726506824973827</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-80.97</t>
+          <t>-0.809748218679889</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>-85</t>
+          <t>-0.850004131088657</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>-86</t>
+          <t>-0.859983109002422</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>-84.6</t>
+          <t>-0.845976224959313</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>-85.15</t>
+          <t>-0.851486957584306</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>-74.7</t>
+          <t>-0.747029584830714</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>78.12</t>
+          <t>0.781178371718612</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>75.14</t>
+          <t>0.75143352341223</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>121.47</t>
+          <t>1.21469464155329</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>62.65</t>
+          <t>0.626464607894378</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>96.15</t>
+          <t>0.96153403466011</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>33.59</t>
+          <t>0.335865861780761</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>9.97</t>
+          <t>0.0997493527669158</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>0.0814142660982953</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>31.56</t>
+          <t>0.315571951519204</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>32.7</t>
+          <t>0.327026367507957</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>-12.27</t>
+          <t>-0.122674404137412</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>-21.59</t>
+          <t>-0.215867246867585</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>-64.47</t>
+          <t>-0.644720893386967</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>-69.08</t>
+          <t>-0.690848593958837</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>-43.95</t>
+          <t>-0.439453496371339</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>123.02</t>
+          <t>1.23020879470345</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>87.93</t>
+          <t>0.879295380002146</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>121.24</t>
+          <t>1.212401164715</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>116.66</t>
+          <t>1.16657675677281</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>132.53</t>
+          <t>1.32529846459041</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>65.9</t>
+          <t>0.658999436582803</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>57.53</t>
+          <t>0.575324046391259</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>47.67</t>
+          <t>0.476733899737618</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>32.16</t>
+          <t>0.321551086450686</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>46.18</t>
+          <t>0.461847935001553</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>37.49</t>
+          <t>0.374905783085527</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>28.51</t>
+          <t>0.28506609984422</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>0.217536190157214</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>11.37</t>
+          <t>0.113733326639034</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>0.43995279140132</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>14.83</t>
+          <t>0.148329168489382</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>18.02</t>
+          <t>0.180181561261614</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>22.65</t>
+          <t>0.226542244829683</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-8.36</t>
+          <t>-0.0836234943499569</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-11.54</t>
+          <t>-0.115413659660583</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-40.64</t>
+          <t>-0.406407172150914</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>-48.36</t>
+          <t>-0.483646051646479</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>-49.91</t>
+          <t>-0.499096116965571</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>-59.15</t>
+          <t>-0.591468428148977</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-72.47</t>
+          <t>-0.724744691167766</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>-75.05</t>
+          <t>-0.750456162634618</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>-75.07</t>
+          <t>-0.75067925084895</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>-77.79</t>
+          <t>-0.777930326210093</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>-71.1</t>
+          <t>-0.710950806225868</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>-68.46</t>
+          <t>-0.684558781350064</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>-85.31</t>
+          <t>-0.853136559992003</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>-84.69</t>
+          <t>-0.846875002906231</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>-79.98</t>
+          <t>-0.799787714482617</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-80.49</t>
+          <t>-0.804947099767395</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-85.39</t>
+          <t>-0.853855524178246</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-88.47</t>
+          <t>-0.884714963628377</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>-89.12</t>
+          <t>-0.891210331597748</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>-89.33</t>
+          <t>-0.893333867547047</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>-90.74</t>
+          <t>-0.907432698145861</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-91.07</t>
+          <t>-0.910745710755012</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>-92.08</t>
+          <t>-0.920767650032293</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>-92.23</t>
+          <t>-0.922261508272986</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>-90.88</t>
+          <t>-0.908788577493243</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>-92.92</t>
+          <t>-0.92923381710231</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>-89.89</t>
+          <t>-0.898885444805704</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>-89.26</t>
+          <t>-0.892610579388682</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>-89.25</t>
+          <t>-0.892483168808048</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>-86.52</t>
+          <t>-0.865220042225838</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-87.78</t>
+          <t>-0.877774716414746</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-90.21</t>
+          <t>-0.902113440910329</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-92.88</t>
+          <t>-0.928767986123409</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>-93.16</t>
+          <t>-0.931610014411681</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>-92.98</t>
+          <t>-0.92977196598584</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>-94.15</t>
+          <t>-0.941507053931119</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-94.11</t>
+          <t>-0.941069721134584</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>-94.71</t>
+          <t>-0.947142011033409</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>-94.21</t>
+          <t>-0.942064115967796</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>-93.61</t>
+          <t>-0.936076619485636</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>-92.37</t>
+          <t>-0.923690906035217</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>-89.66</t>
+          <t>-0.896615759008015</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>38.48</t>
+          <t>0.384767808454867</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>20.69</t>
+          <t>0.206917274170808</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-0.0208665964723596</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-0.0605939731723335</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-29.1</t>
+          <t>-0.290995760251048</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-41.24</t>
+          <t>-0.412356809385271</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>-14.47</t>
+          <t>-0.144687843153598</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>47.02</t>
+          <t>0.470237920709798</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>46.74</t>
+          <t>0.467397862997169</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>55.39</t>
+          <t>0.553895052367298</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>35.99</t>
+          <t>0.359871435893152</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>42.73</t>
+          <t>0.427270605471899</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>59.66</t>
+          <t>0.596575183821573</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>0.571449207117735</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>175.98</t>
+          <t>1.7598134552849</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>-74.66</t>
+          <t>-0.746612189465532</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>-75.97</t>
+          <t>-0.75971008422223</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>-71.23</t>
+          <t>-0.712338659360383</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-72.45</t>
+          <t>-0.724459154505337</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-80.07</t>
+          <t>-0.800713737933811</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-85.77</t>
+          <t>-0.857741886402898</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>-85.37</t>
+          <t>-0.853731995671135</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>-86.77</t>
+          <t>-0.867663795135374</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>-86.86</t>
+          <t>-0.868607875405683</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-85.55</t>
+          <t>-0.855471056710801</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>-86.01</t>
+          <t>-0.86005802130875</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>-84.67</t>
+          <t>-0.846728363222668</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>-78.83</t>
+          <t>-0.788306798507914</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>-77.1</t>
+          <t>-0.770986599592613</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>-66.47</t>
+          <t>-0.664737506000509</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>-74.23</t>
+          <t>-0.742347715830225</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-71.87</t>
+          <t>-0.718678247585998</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>-69.46</t>
+          <t>-0.694606293971859</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-71.86</t>
+          <t>-0.718613091740416</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-75.48</t>
+          <t>-0.754775879503866</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-83.5</t>
+          <t>-0.83496718910577</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>-83.43</t>
+          <t>-0.83429846602295</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>-82.66</t>
+          <t>-0.826562575751111</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>-82.51</t>
+          <t>-0.825077307738148</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-84.43</t>
+          <t>-0.844272185545126</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>-86.42</t>
+          <t>-0.864221348951387</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>-85.74</t>
+          <t>-0.857399597648638</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>-84.02</t>
+          <t>-0.840209200108395</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>-83.33</t>
+          <t>-0.833320971579535</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>-74.99</t>
+          <t>-0.749919436142135</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>792.97</t>
+          <t>7.92973090971327</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>750.6</t>
+          <t>7.50596302412468</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>688.56</t>
+          <t>6.885613759464</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>732.3</t>
+          <t>7.32299328430618</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>757.76</t>
+          <t>7.57764883421804</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>709.55</t>
+          <t>7.09546803073044</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>704.54</t>
+          <t>7.04541469412604</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>709.62</t>
+          <t>7.09624339067863</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>741.46</t>
+          <t>7.41457374521703</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>696.33</t>
+          <t>6.9632719684586</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>705.8</t>
+          <t>7.05796072785043</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>693.27</t>
+          <t>6.93265776992831</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>721.06</t>
+          <t>7.21056827194889</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>646.37</t>
+          <t>6.46372137871951</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>630.98</t>
+          <t>6.30979085386696</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>433.82</t>
+          <t>4.33819058379071</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>408.65</t>
+          <t>4.08654811468699</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>413.67</t>
+          <t>4.13672101703066</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>439.36</t>
+          <t>4.39357500145542</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>432.19</t>
+          <t>4.32194418148879</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>374.54</t>
+          <t>3.7454419755148</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>367.62</t>
+          <t>3.67618112309421</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>362.26</t>
+          <t>3.62263295520496</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>373.76</t>
+          <t>3.73757791418219</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>336.24</t>
+          <t>3.36239572953374</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>318.05</t>
+          <t>3.18051633279474</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>303.48</t>
+          <t>3.0348354533439</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>308.78</t>
+          <t>3.08779084768266</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>275.56</t>
+          <t>2.75564814605235</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>313.65</t>
+          <t>3.13651690402181</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO2</t>
